--- a/it_forms/014_inventory_management_system_requirements_questionnaire--it_forms.xlsx
+++ b/it_forms/014_inventory_management_system_requirements_questionnaire--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Evaluation Criteria</t>
+          <t>Evaluation Criteria 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evaluation Method</t>
+          <t>Evaluation Method 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>System Implementation Plan</t>
+          <t>System Implementation Plan 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Implementation Details</t>
+          <t>Implementation Details 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>value1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Value1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>value2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Value2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>value3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Value3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>value1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Value1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>value2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Value2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>value3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Value3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>value1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Value1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>value2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Value2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>value3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Value3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
